--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454373.4581992469</v>
+        <v>454373</v>
       </c>
       <c r="R2" t="n">
-        <v>6239109.357872237</v>
+        <v>6239109</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -744,19 +739,9 @@
           <t>2002-07-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-07-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,12 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454373.4581992469</v>
+        <v>454373</v>
       </c>
       <c r="R3" t="n">
-        <v>6239109.357872237</v>
+        <v>6239109</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -875,19 +855,9 @@
           <t>2002-07-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-07-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101848</v>
+        <v>101853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101853</v>
+        <v>101859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101859</v>
+        <v>101860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101860</v>
+        <v>101887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101887</v>
+        <v>101893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101893</v>
+        <v>101900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101900</v>
+        <v>101904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101904</v>
+        <v>101911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101914</v>
+        <v>101919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101919</v>
+        <v>101927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>63016926</v>
       </c>
       <c r="B3" t="n">
-        <v>101927</v>
+        <v>101937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98589</v>
+        <v>98877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98877</v>
+        <v>98890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98890</v>
+        <v>98891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98891</v>
+        <v>98894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98894</v>
+        <v>98908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63016934</v>
       </c>
       <c r="B2" t="n">
-        <v>98908</v>
+        <v>98909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37585-2024 artfynd.xlsx
+++ b/artfynd/A 37585-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63016926</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63016934</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>